--- a/xls/square_un_16_tri3_15.xlsx
+++ b/xls/square_un_16_tri3_15.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>297</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>340</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>238</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1266</v>
+      </c>
+      <c r="I13">
+        <v>-0.0002057017779106672</v>
+      </c>
+      <c r="J13">
+        <v>-1.1655503023658957</v>
+      </c>
+      <c r="K13">
+        <v>0.9889576365153936</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>297</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>340</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>256</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>1362</v>
+      </c>
+      <c r="I14">
+        <v>-0.00019058321178449505</v>
+      </c>
+      <c r="J14">
+        <v>-0.9342530944111181</v>
+      </c>
+      <c r="K14">
+        <v>1.4379542412977055</v>
+      </c>
+    </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="B15">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F15">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15">
-        <v>1350</v>
+        <v>1596</v>
       </c>
       <c r="I15">
-        <v>-1.8758381780269475</v>
+        <v>-0.00018361185933426773</v>
       </c>
       <c r="J15">
-        <v>-2.014363030090022</v>
+        <v>-0.8611754370832159</v>
       </c>
       <c r="K15">
-        <v>-0.800017644785798</v>
+        <v>1.6600683590292928</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F16">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1536</v>
+        <v>1842</v>
       </c>
       <c r="I16">
-        <v>-2.344673152406465</v>
+        <v>-0.00011937443262114191</v>
       </c>
       <c r="J16">
-        <v>-2.1340790575003554</v>
+        <v>-0.422251406538711</v>
       </c>
       <c r="K16">
-        <v>-0.6517357161932814</v>
+        <v>2.720367001440412</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B17">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F17">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17">
-        <v>1734</v>
+        <v>2070</v>
       </c>
       <c r="I17">
-        <v>-2.5758283892362517</v>
+        <v>-5.968616639014764e-5</v>
       </c>
       <c r="J17">
-        <v>-2.0943568534672057</v>
+        <v>-0.17198199282716148</v>
       </c>
       <c r="K17">
-        <v>-0.306509657132219</v>
+        <v>2.9576762822003535</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B18">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>361</v>
+        <v>435</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>1944</v>
+        <v>2388</v>
       </c>
       <c r="I18">
-        <v>-2.1003607487890243</v>
+        <v>-8.780918293184494e-7</v>
       </c>
       <c r="J18">
-        <v>-1.7659627337212742</v>
+        <v>-0.002838322838784704</v>
       </c>
       <c r="K18">
-        <v>0.4407324721652056</v>
+        <v>3.0234370632912624</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B19">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>2166</v>
+        <v>2676</v>
       </c>
       <c r="I19">
-        <v>-1.4974631506987488</v>
+        <v>-7.841804036676375e-9</v>
       </c>
       <c r="J19">
-        <v>-1.2814302379092832</v>
+        <v>-1.3341782522643835e-5</v>
       </c>
       <c r="K19">
-        <v>1.0692890958509143</v>
+        <v>1.9651912176305755</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B20">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>-0.3204535556283035</v>
+        <v>-1.1096302091106726e-9</v>
       </c>
       <c r="J20">
-        <v>-0.2800400355536643</v>
+        <v>-1.7558359142558472e-6</v>
       </c>
       <c r="K20">
-        <v>2.604119018474592</v>
+        <v>1.5416540516941786</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B21">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-0.008925636129583721</v>
+        <v>-1.073893101005089e-9</v>
       </c>
       <c r="J21">
-        <v>-0.013308470708061246</v>
+        <v>-1.5598729686439152e-6</v>
       </c>
       <c r="K21">
-        <v>3.1776923105239003</v>
+        <v>1.5033839362521375</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-0.0001317303885881584</v>
+        <v>-5.551611048963871e-10</v>
       </c>
       <c r="J22">
-        <v>-0.00015110689628297468</v>
+        <v>-8.748774237705985e-7</v>
       </c>
       <c r="K22">
-        <v>2.583490637590021</v>
+        <v>1.3944696402014822</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-3.0083792965189655e-5</v>
+        <v>-4.0216953961524587e-10</v>
       </c>
       <c r="J23">
-        <v>-3.971321007391722e-5</v>
+        <v>-6.613660357207494e-7</v>
       </c>
       <c r="K23">
-        <v>2.313983911097994</v>
+        <v>1.3402694840035712</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-2.0597815333688025e-5</v>
+        <v>-3.3463416727997757e-10</v>
       </c>
       <c r="J24">
-        <v>-2.57133556442465e-5</v>
+        <v>-5.519122136230315e-7</v>
       </c>
       <c r="K24">
-        <v>2.208710903173569</v>
+        <v>1.3019238459523501</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-1.5709293361283228e-5</v>
+        <v>-3.0945393775290615e-10</v>
       </c>
       <c r="J25">
-        <v>-1.814524770531475e-5</v>
+        <v>-5.154686194488301e-7</v>
       </c>
       <c r="K25">
-        <v>2.1202323400390894</v>
+        <v>1.2887806397938664</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -846,7 +916,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-1.1206396978587094e-5</v>
+        <v>-2.746454770640444e-10</v>
       </c>
       <c r="J26">
-        <v>-1.3058909328333265e-5</v>
+        <v>-4.5289626436963283e-7</v>
       </c>
       <c r="K26">
-        <v>2.050930379198649</v>
+        <v>1.2591785563393</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -881,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-9.306524877566263e-6</v>
+        <v>-2.4127497328052e-10</v>
       </c>
       <c r="J27">
-        <v>-1.0656548297415436e-5</v>
+        <v>-4.056907630870869e-7</v>
       </c>
       <c r="K27">
-        <v>2.002681887243706</v>
+        <v>1.2381400568874423</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -916,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -928,22 +998,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-9.343756637852686e-6</v>
+        <v>-2.4477813388660173e-10</v>
       </c>
       <c r="J28">
-        <v>-1.076404896637674e-5</v>
+        <v>-4.0737962655812796e-7</v>
       </c>
       <c r="K28">
-        <v>2.007320954757417</v>
+        <v>1.238044308734925</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -951,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -963,22 +1033,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-4.693231900462033e-6</v>
+        <v>-2.5524803006249136e-10</v>
       </c>
       <c r="J29">
-        <v>-5.575771225082858e-6</v>
+        <v>-4.260939924492775e-7</v>
       </c>
       <c r="K29">
-        <v>1.8655265663432852</v>
+        <v>1.2479106575273553</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -986,7 +1056,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -998,22 +1068,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-5.075551268472209e-6</v>
+        <v>-2.1531040801355078e-10</v>
       </c>
       <c r="J30">
-        <v>-5.585611840134806e-6</v>
+        <v>-3.607738088938027e-7</v>
       </c>
       <c r="K30">
-        <v>1.8519781499673909</v>
+        <v>1.2126307394430729</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1021,7 +1091,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -1033,22 +1103,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-3.4544463727625863e-6</v>
+        <v>-2.2223172375910353e-10</v>
       </c>
       <c r="J31">
-        <v>-4.052469014583408e-6</v>
+        <v>-3.725595737383836e-7</v>
       </c>
       <c r="K31">
-        <v>1.7969597329508478</v>
+        <v>1.218673152381136</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1056,7 +1126,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1068,22 +1138,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-3.269110613155307e-6</v>
+        <v>-2.092824934499262e-10</v>
       </c>
       <c r="J32">
-        <v>-3.6905794227339485e-6</v>
+        <v>-3.4955446064320763e-7</v>
       </c>
       <c r="K32">
-        <v>1.7695562455424028</v>
+        <v>1.2055217821863318</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_15.xlsx
+++ b/xls/square_un_16_tri3_15.xlsx
@@ -482,13 +482,13 @@
         <v>1266</v>
       </c>
       <c r="I13">
-        <v>-0.0002057017779106672</v>
+        <v>-1.3558150314925452</v>
       </c>
       <c r="J13">
-        <v>-1.1655503023658957</v>
+        <v>-1.8541422391666784</v>
       </c>
       <c r="K13">
-        <v>0.9889576365153936</v>
+        <v>-0.8043729510114928</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1362</v>
       </c>
       <c r="I14">
-        <v>-0.00019058321178449505</v>
+        <v>-2.1601530669456737</v>
       </c>
       <c r="J14">
-        <v>-0.9342530944111181</v>
+        <v>-1.9455224095178387</v>
       </c>
       <c r="K14">
-        <v>1.4379542412977055</v>
+        <v>-0.8856668776236495</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1596</v>
       </c>
       <c r="I15">
-        <v>-0.00018361185933426773</v>
+        <v>-2.1897871616776214</v>
       </c>
       <c r="J15">
-        <v>-0.8611754370832159</v>
+        <v>-1.8701600196435233</v>
       </c>
       <c r="K15">
-        <v>1.6600683590292928</v>
+        <v>-0.4894484102927914</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-0.00011937443262114191</v>
+        <v>-2.010657704088699</v>
       </c>
       <c r="J16">
-        <v>-0.422251406538711</v>
+        <v>-1.6798620903223909</v>
       </c>
       <c r="K16">
-        <v>2.720367001440412</v>
+        <v>-0.3120919626633557</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2070</v>
       </c>
       <c r="I17">
-        <v>-5.968616639014764e-5</v>
+        <v>-0.8940167364231975</v>
       </c>
       <c r="J17">
-        <v>-0.17198199282716148</v>
+        <v>-0.7737102468080341</v>
       </c>
       <c r="K17">
-        <v>2.9576762822003535</v>
+        <v>1.1440249714202484</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -657,13 +657,13 @@
         <v>2388</v>
       </c>
       <c r="I18">
-        <v>-8.780918293184494e-7</v>
+        <v>-0.33490955381992354</v>
       </c>
       <c r="J18">
-        <v>-0.002838322838784704</v>
+        <v>-0.30740728775603415</v>
       </c>
       <c r="K18">
-        <v>3.0234370632912624</v>
+        <v>1.9177864814302168</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -692,13 +692,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-7.841804036676375e-9</v>
+        <v>0.001355535661202078</v>
       </c>
       <c r="J19">
-        <v>-1.3341782522643835e-5</v>
+        <v>0.00018484294348128954</v>
       </c>
       <c r="K19">
-        <v>1.9651912176305755</v>
+        <v>2.7000786228900515</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -727,13 +727,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-1.1096302091106726e-9</v>
+        <v>4.954611925435361e-6</v>
       </c>
       <c r="J20">
-        <v>-1.7558359142558472e-6</v>
+        <v>2.4578770673401866e-7</v>
       </c>
       <c r="K20">
-        <v>1.5416540516941786</v>
+        <v>1.8040918017086112</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -762,13 +762,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.073893101005089e-9</v>
+        <v>1.502269914037886e-6</v>
       </c>
       <c r="J21">
-        <v>-1.5598729686439152e-6</v>
+        <v>-9.302355206365958e-7</v>
       </c>
       <c r="K21">
-        <v>1.5033839362521375</v>
+        <v>1.756648893464172</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -797,13 +797,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-5.551611048963871e-10</v>
+        <v>-5.864464573434526e-7</v>
       </c>
       <c r="J22">
-        <v>-8.748774237705985e-7</v>
+        <v>-8.250121271393122e-7</v>
       </c>
       <c r="K22">
-        <v>1.3944696402014822</v>
+        <v>1.4802177521581574</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -832,13 +832,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-4.0216953961524587e-10</v>
+        <v>-4.772232961008173e-7</v>
       </c>
       <c r="J23">
-        <v>-6.613660357207494e-7</v>
+        <v>-6.471238004842997e-7</v>
       </c>
       <c r="K23">
-        <v>1.3402694840035712</v>
+        <v>1.4185116756445144</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -867,13 +867,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-3.3463416727997757e-10</v>
+        <v>-3.638745791589541e-7</v>
       </c>
       <c r="J24">
-        <v>-5.519122136230315e-7</v>
+        <v>-4.803624870104819e-7</v>
       </c>
       <c r="K24">
-        <v>1.3019238459523501</v>
+        <v>1.3549617040990578</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -902,13 +902,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-3.0945393775290615e-10</v>
+        <v>-4.7013245509068615e-7</v>
       </c>
       <c r="J25">
-        <v>-5.154686194488301e-7</v>
+        <v>-5.030731906230987e-7</v>
       </c>
       <c r="K25">
-        <v>1.2887806397938664</v>
+        <v>1.3269468470143555</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -937,13 +937,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-2.746454770640444e-10</v>
+        <v>-3.4360071113189305e-7</v>
       </c>
       <c r="J26">
-        <v>-4.5289626436963283e-7</v>
+        <v>-4.016666666343003e-7</v>
       </c>
       <c r="K26">
-        <v>1.2591785563393</v>
+        <v>1.294494413952085</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -972,13 +972,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-2.4127497328052e-10</v>
+        <v>-3.269953163700683e-7</v>
       </c>
       <c r="J27">
-        <v>-4.056907630870869e-7</v>
+        <v>-3.6756713509944615e-7</v>
       </c>
       <c r="K27">
-        <v>1.2381400568874423</v>
+        <v>1.268784830930779</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-2.4477813388660173e-10</v>
+        <v>-3.1292517766472934e-7</v>
       </c>
       <c r="J28">
-        <v>-4.0737962655812796e-7</v>
+        <v>-3.57088282530134e-7</v>
       </c>
       <c r="K28">
-        <v>1.238044308734925</v>
+        <v>1.2659506288856177</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-2.5524803006249136e-10</v>
+        <v>-3.357390277710846e-7</v>
       </c>
       <c r="J29">
-        <v>-4.260939924492775e-7</v>
+        <v>-3.748263216619716e-7</v>
       </c>
       <c r="K29">
-        <v>1.2479106575273553</v>
+        <v>1.2700949793154326</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-2.1531040801355078e-10</v>
+        <v>-2.615981063946461e-7</v>
       </c>
       <c r="J30">
-        <v>-3.607738088938027e-7</v>
+        <v>-3.1066801307528075e-7</v>
       </c>
       <c r="K30">
-        <v>1.2126307394430729</v>
+        <v>1.2423139541873014</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-2.2223172375910353e-10</v>
+        <v>-3.045919467867442e-7</v>
       </c>
       <c r="J31">
-        <v>-3.725595737383836e-7</v>
+        <v>-3.3315648628630075e-7</v>
       </c>
       <c r="K31">
-        <v>1.218673152381136</v>
+        <v>1.2403628006882745</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-2.092824934499262e-10</v>
+        <v>-2.76601541946451e-7</v>
       </c>
       <c r="J32">
-        <v>-3.4955446064320763e-7</v>
+        <v>-3.0813261441593743e-7</v>
       </c>
       <c r="K32">
-        <v>1.2055217821863318</v>
+        <v>1.2285661066945952</v>
       </c>
     </row>
   </sheetData>
